--- a/data/trans_dic/P38B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,24; 87,97</t>
+          <t>79,33; 87,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,73; 75,97</t>
+          <t>64,79; 75,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,09; 98,53</t>
+          <t>92,94; 98,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,35; 93,15</t>
+          <t>85,73; 92,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,74; 80,12</t>
+          <t>69,49; 80,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,21; 99,34</t>
+          <t>95,99; 99,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,46; 89,66</t>
+          <t>83,46; 89,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,06; 76,5</t>
+          <t>68,86; 76,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95,5; 98,66</t>
+          <t>95,28; 98,61</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,01; 89,6</t>
+          <t>83,82; 89,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,13; 91,37</t>
+          <t>85,41; 91,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,4; 80,44</t>
+          <t>68,85; 81,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91,04; 95,39</t>
+          <t>91,09; 95,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,52; 96,64</t>
+          <t>92,65; 96,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,33; 87,34</t>
+          <t>80,76; 87,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,2; 91,89</t>
+          <t>88,27; 92,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,76; 93,3</t>
+          <t>89,99; 93,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>75,73; 83,2</t>
+          <t>76,46; 83,1</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,19; 88,09</t>
+          <t>80,03; 88,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,15; 92,62</t>
+          <t>85,56; 92,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,11; 96,05</t>
+          <t>89,2; 96,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,82; 91,54</t>
+          <t>84,89; 91,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,33; 95,08</t>
+          <t>88,78; 94,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>94,55; 98,74</t>
+          <t>94,53; 98,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,23; 88,78</t>
+          <t>83,65; 88,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88,48; 92,83</t>
+          <t>88,58; 92,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93,04; 96,81</t>
+          <t>92,93; 97,0</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,22; 81,18</t>
+          <t>72,22; 81,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,25; 94,21</t>
+          <t>88,39; 93,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,12; 93,26</t>
+          <t>79,58; 92,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81,54; 88,48</t>
+          <t>80,89; 88,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,71; 94,01</t>
+          <t>88,32; 93,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,13; 94,64</t>
+          <t>50,59; 94,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,91; 83,78</t>
+          <t>77,65; 83,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89,4; 93,21</t>
+          <t>89,34; 93,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,03; 92,3</t>
+          <t>60,92; 92,17</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,5; 88,1</t>
+          <t>78,22; 89,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,41; 82,92</t>
+          <t>71,19; 82,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,14; 86,83</t>
+          <t>75,59; 86,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88,32; 95,16</t>
+          <t>87,83; 95,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,19; 92,42</t>
+          <t>84,07; 92,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,89; 91,71</t>
+          <t>83,43; 91,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,44; 90,81</t>
+          <t>84,52; 90,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,43; 86,37</t>
+          <t>79,51; 86,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81,67; 88,31</t>
+          <t>81,71; 88,37</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,62; 91,38</t>
+          <t>83,58; 91,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75,5; 85,62</t>
+          <t>75,74; 85,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,11; 98,01</t>
+          <t>92,15; 98,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83,9; 92,0</t>
+          <t>83,95; 91,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82,06; 90,43</t>
+          <t>82,56; 90,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94,48; 98,94</t>
+          <t>94,18; 98,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,15; 90,49</t>
+          <t>85,24; 90,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80,35; 86,87</t>
+          <t>80,47; 86,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94,32; 97,93</t>
+          <t>94,51; 97,97</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,56; 88,48</t>
+          <t>82,82; 88,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61,61; 69,81</t>
+          <t>62,3; 70,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,13; 86,53</t>
+          <t>77,14; 86,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90,05; 94,04</t>
+          <t>90,19; 94,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,15; 76,77</t>
+          <t>69,86; 76,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,35; 97,05</t>
+          <t>90,0; 97,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,17; 90,73</t>
+          <t>87,3; 90,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,18; 72,55</t>
+          <t>67,05; 72,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,64; 93,11</t>
+          <t>85,69; 93,03</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>71,07; 77,43</t>
+          <t>70,77; 77,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86,94; 91,35</t>
+          <t>87,02; 91,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,09; 62,94</t>
+          <t>21,4; 63,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,57; 82,22</t>
+          <t>76,31; 82,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,55; 95,77</t>
+          <t>92,89; 96,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,23; 73,57</t>
+          <t>67,29; 73,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,69; 79,14</t>
+          <t>74,71; 79,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,55; 93,31</t>
+          <t>90,6; 93,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35,47; 66,71</t>
+          <t>34,65; 66,91</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>80,74; 83,42</t>
+          <t>80,79; 83,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>80,45; 83,16</t>
+          <t>80,42; 83,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57,8; 81,59</t>
+          <t>57,56; 81,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86,58; 88,89</t>
+          <t>86,6; 88,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86,37; 88,53</t>
+          <t>86,3; 88,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81,36; 88,93</t>
+          <t>80,89; 88,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,15; 85,87</t>
+          <t>84,08; 85,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83,85; 85,63</t>
+          <t>83,83; 85,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71,59; 84,8</t>
+          <t>70,31; 84,79</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>229227; 254500</t>
+          <t>229510; 254204</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>187004; 219489</t>
+          <t>187187; 218150</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>289925; 306865</t>
+          <t>289461; 306548</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>244154; 266469</t>
+          <t>245260; 265758</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>200736; 230586</t>
+          <t>200008; 230332</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>278645; 287713</t>
+          <t>278035; 287749</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>480193; 515889</t>
+          <t>480199; 514858</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>398311; 441214</t>
+          <t>397170; 442615</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>574057; 592993</t>
+          <t>572687; 592745</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>422978; 451153</t>
+          <t>422038; 450688</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>421852; 452767</t>
+          <t>423249; 451055</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>359057; 416194</t>
+          <t>356202; 419251</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>475004; 497688</t>
+          <t>475253; 498395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>483033; 504543</t>
+          <t>483708; 504325</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>413212; 449282</t>
+          <t>415457; 449689</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>904285; 942127</t>
+          <t>905007; 943786</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>913444; 949500</t>
+          <t>915834; 950458</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>781425; 858410</t>
+          <t>788870; 857412</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>259844; 285437</t>
+          <t>259349; 286023</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>274452; 295046</t>
+          <t>272569; 293588</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>281635; 303561</t>
+          <t>281905; 303635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>289248; 312163</t>
+          <t>289501; 312497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>299611; 318890</t>
+          <t>297760; 317594</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>330105; 344743</t>
+          <t>330037; 344754</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>553511; 590424</t>
+          <t>556346; 590976</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>578636; 607045</t>
+          <t>579285; 606783</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>618894; 643966</t>
+          <t>618135; 645247</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>267762; 300975</t>
+          <t>267755; 302350</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>323837; 345710</t>
+          <t>324337; 344641</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>247292; 291504</t>
+          <t>248719; 290397</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>314514; 341282</t>
+          <t>311992; 340810</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>338620; 362938</t>
+          <t>340981; 362407</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>228781; 449871</t>
+          <t>240465; 451135</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>589380; 633761</t>
+          <t>587433; 632585</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>673217; 701879</t>
+          <t>672765; 702692</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>465107; 727203</t>
+          <t>479990; 726216</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>163978; 186399</t>
+          <t>165493; 188374</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>150837; 175154</t>
+          <t>150363; 175013</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134314; 155205</t>
+          <t>135107; 155037</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>192992; 207942</t>
+          <t>191914; 208646</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>184022; 202028</t>
+          <t>183765; 202129</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>174713; 191012</t>
+          <t>173763; 190664</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>363192; 390575</t>
+          <t>363511; 391085</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>341413; 371232</t>
+          <t>341758; 372791</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>316058; 341784</t>
+          <t>316225; 342003</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>229093; 250360</t>
+          <t>228983; 250629</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>197867; 224412</t>
+          <t>198493; 223197</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>248372; 264274</t>
+          <t>248466; 264375</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>234129; 256724</t>
+          <t>234258; 256201</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>222689; 245392</t>
+          <t>224041; 246017</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>241825; 253256</t>
+          <t>241070; 253107</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>470918; 500457</t>
+          <t>471396; 501724</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>428658; 463407</t>
+          <t>429298; 462452</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>495743; 514730</t>
+          <t>496723; 514946</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>542983; 581875</t>
+          <t>544685; 581177</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>399841; 453040</t>
+          <t>404283; 455547</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>480928; 539497</t>
+          <t>480953; 539617</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622075; 649664</t>
+          <t>623048; 649709</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>482735; 528301</t>
+          <t>480727; 527640</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>766530; 823399</t>
+          <t>763580; 825390</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1175490; 1223506</t>
+          <t>1177205; 1222892</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>898240; 970019</t>
+          <t>896556; 969824</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1260542; 1370518</t>
+          <t>1261216; 1369371</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>548699; 597776</t>
+          <t>546323; 597235</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>671082; 705110</t>
+          <t>671744; 705147</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>186566; 584551</t>
+          <t>198780; 587782</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>624449; 670531</t>
+          <t>622355; 673346</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>762801; 789380</t>
+          <t>765628; 791330</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>482136; 527610</t>
+          <t>482576; 527265</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1185805; 1256362</t>
+          <t>1186057; 1256442</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1445234; 1489326</t>
+          <t>1446141; 1486459</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>583805; 1097990</t>
+          <t>570326; 1101346</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2747559; 2838568</t>
+          <t>2749310; 2837390</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2706648; 2797584</t>
+          <t>2705454; 2799000</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1998847; 2821310</t>
+          <t>1990444; 2821953</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3063703; 3145389</t>
+          <t>3064325; 3144046</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3052190; 3128441</t>
+          <t>3049687; 3126251</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2976473; 3253470</t>
+          <t>2959067; 3249668</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5841085; 5960478</t>
+          <t>5836035; 5956632</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5783798; 5906573</t>
+          <t>5782206; 5902103</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5094912; 6034595</t>
+          <t>5003784; 6034223</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,33; 87,87</t>
+          <t>79,32; 88,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,79; 75,51</t>
+          <t>64,4; 76,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,94; 98,43</t>
+          <t>94,54; 98,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,73; 92,9</t>
+          <t>85,65; 92,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,49; 80,03</t>
+          <t>69,34; 79,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,99; 99,35</t>
+          <t>97,04; 99,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,46; 89,48</t>
+          <t>83,73; 89,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,86; 76,74</t>
+          <t>68,78; 76,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95,28; 98,61</t>
+          <t>96,47; 98,86</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>83,82; 89,51</t>
+          <t>84,01; 89,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,41; 91,02</t>
+          <t>85,33; 90,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,85; 81,03</t>
+          <t>70,21; 81,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91,09; 95,53</t>
+          <t>91,06; 95,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,65; 96,6</t>
+          <t>92,71; 96,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,76; 87,42</t>
+          <t>79,85; 87,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,27; 92,06</t>
+          <t>88,22; 91,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,99; 93,4</t>
+          <t>89,91; 93,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76,46; 83,1</t>
+          <t>76,82; 83,22</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,03; 88,27</t>
+          <t>80,26; 87,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,56; 92,16</t>
+          <t>85,44; 92,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,2; 96,07</t>
+          <t>89,57; 96,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,89; 91,64</t>
+          <t>83,91; 91,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,78; 94,69</t>
+          <t>89,15; 94,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>94,53; 98,75</t>
+          <t>94,32; 98,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,65; 88,86</t>
+          <t>83,77; 89,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88,58; 92,79</t>
+          <t>88,83; 93,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92,93; 97,0</t>
+          <t>93,25; 97,0</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,22; 81,55</t>
+          <t>72,33; 81,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88,39; 93,92</t>
+          <t>88,13; 94,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79,58; 92,91</t>
+          <t>78,49; 91,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,89; 88,36</t>
+          <t>81,35; 88,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,32; 93,87</t>
+          <t>88,29; 94,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,59; 94,91</t>
+          <t>88,93; 95,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,65; 83,62</t>
+          <t>77,87; 83,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89,34; 93,31</t>
+          <t>89,26; 93,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,92; 92,17</t>
+          <t>85,85; 92,37</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,22; 89,03</t>
+          <t>77,73; 88,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,19; 82,86</t>
+          <t>71,46; 83,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,59; 86,74</t>
+          <t>72,32; 83,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,83; 95,48</t>
+          <t>88,61; 95,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,07; 92,47</t>
+          <t>84,29; 92,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,43; 91,54</t>
+          <t>81,89; 90,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,52; 90,93</t>
+          <t>84,19; 91,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,51; 86,73</t>
+          <t>79,23; 86,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81,71; 88,37</t>
+          <t>78,76; 85,97</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83,58; 91,48</t>
+          <t>83,64; 91,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75,74; 85,16</t>
+          <t>74,71; 84,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,15; 98,05</t>
+          <t>90,39; 96,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83,95; 91,81</t>
+          <t>83,83; 91,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82,56; 90,66</t>
+          <t>82,72; 90,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>94,18; 98,88</t>
+          <t>93,95; 98,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,24; 90,72</t>
+          <t>85,14; 91,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80,47; 86,69</t>
+          <t>80,37; 86,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94,51; 97,97</t>
+          <t>93,43; 97,13</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,82; 88,37</t>
+          <t>82,75; 88,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,3; 70,19</t>
+          <t>62,11; 69,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,14; 86,55</t>
+          <t>79,74; 87,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90,19; 94,05</t>
+          <t>90,01; 94,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,86; 76,68</t>
+          <t>69,67; 76,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,0; 97,29</t>
+          <t>88,65; 93,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,3; 90,69</t>
+          <t>87,36; 90,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>67,05; 72,53</t>
+          <t>67,11; 72,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85,69; 93,03</t>
+          <t>85,15; 89,59</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>64,54%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>70,77; 77,36</t>
+          <t>71,01; 77,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,02; 91,35</t>
+          <t>86,81; 91,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,4; 63,29</t>
+          <t>55,8; 63,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,31; 82,56</t>
+          <t>76,35; 82,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,89; 96,01</t>
+          <t>92,8; 95,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,29; 73,52</t>
+          <t>65,84; 72,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,71; 79,14</t>
+          <t>74,66; 79,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,6; 93,13</t>
+          <t>90,62; 93,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,65; 66,91</t>
+          <t>62,15; 67,07</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>80,79; 83,38</t>
+          <t>80,77; 83,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>80,42; 83,2</t>
+          <t>80,48; 83,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57,56; 81,61</t>
+          <t>78,27; 81,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86,6; 88,85</t>
+          <t>86,55; 88,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>86,3; 88,47</t>
+          <t>86,23; 88,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>80,89; 88,83</t>
+          <t>85,51; 87,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,08; 85,81</t>
+          <t>84,18; 85,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83,83; 85,56</t>
+          <t>83,79; 85,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>70,31; 84,79</t>
+          <t>82,29; 84,51</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300452</t>
+          <t>309441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>284965</t>
+          <t>311718</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>585416</t>
+          <t>621159</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>229510; 254204</t>
+          <t>229471; 254596</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>187187; 218150</t>
+          <t>186066; 219696</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>289461; 306548</t>
+          <t>301426; 314627</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>245260; 265758</t>
+          <t>245016; 265718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>200008; 230332</t>
+          <t>199578; 229928</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>278035; 287749</t>
+          <t>306704; 314129</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>480199; 514858</t>
+          <t>481775; 515307</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>397170; 442615</t>
+          <t>396696; 439895</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>572687; 592745</t>
+          <t>612505; 627677</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>390202</t>
+          <t>403370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>434115</t>
+          <t>458462</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>824317</t>
+          <t>861832</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>422038; 450688</t>
+          <t>423002; 451717</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423249; 451055</t>
+          <t>422873; 450907</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>356202; 419251</t>
+          <t>371896; 430601</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>475253; 498395</t>
+          <t>475119; 498956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>483708; 504325</t>
+          <t>484022; 504461</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>415457; 449689</t>
+          <t>435883; 475962</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>905007; 943786</t>
+          <t>904471; 941999</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>915834; 950458</t>
+          <t>914998; 950732</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>788870; 857412</t>
+          <t>826280; 895128</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294888</t>
+          <t>295237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>339171</t>
+          <t>345546</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>634059</t>
+          <t>640784</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>259349; 286023</t>
+          <t>260090; 284414</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>272569; 293588</t>
+          <t>272177; 293742</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>281905; 303635</t>
+          <t>283019; 303925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>289501; 312497</t>
+          <t>286162; 312431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>297760; 317594</t>
+          <t>298991; 318185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>330037; 344754</t>
+          <t>336150; 351351</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>556346; 590976</t>
+          <t>557134; 593193</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>579285; 606783</t>
+          <t>580908; 608517</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>618135; 645247</t>
+          <t>626989; 652182</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276343</t>
+          <t>321788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>379795</t>
+          <t>390939</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>656138</t>
+          <t>712728</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>267755; 302350</t>
+          <t>268170; 301938</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>324337; 344641</t>
+          <t>323414; 344971</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>248719; 290397</t>
+          <t>292878; 341063</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311992; 340810</t>
+          <t>313787; 340579</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>340981; 362407</t>
+          <t>340884; 363188</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>240465; 451135</t>
+          <t>374894; 401721</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>587433; 632585</t>
+          <t>589060; 634825</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>672765; 702692</t>
+          <t>672156; 702964</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>479990; 726216</t>
+          <t>682232; 734041</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146412</t>
+          <t>161140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>183687</t>
+          <t>196305</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>330099</t>
+          <t>357445</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>165493; 188374</t>
+          <t>164471; 187402</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>150363; 175013</t>
+          <t>150934; 175327</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>135107; 155037</t>
+          <t>148744; 171451</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>191914; 208646</t>
+          <t>193620; 207779</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>183765; 202129</t>
+          <t>184256; 201688</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>173763; 190664</t>
+          <t>185737; 204997</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>363511; 391085</t>
+          <t>362096; 391385</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>341758; 372791</t>
+          <t>340516; 371095</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>316225; 342003</t>
+          <t>340637; 371819</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258554</t>
+          <t>254240</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>249192</t>
+          <t>255091</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>507746</t>
+          <t>509331</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>228983; 250629</t>
+          <t>229154; 250679</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>198493; 223197</t>
+          <t>195800; 221731</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>248466; 264375</t>
+          <t>244684; 261103</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>234258; 256201</t>
+          <t>233945; 256426</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>224041; 246017</t>
+          <t>224481; 245315</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>241070; 253107</t>
+          <t>246681; 259428</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>471396; 501724</t>
+          <t>470872; 503666</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>429298; 462452</t>
+          <t>428723; 462970</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>496723; 514946</t>
+          <t>498249; 517964</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>513588</t>
+          <t>600152</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>791458</t>
+          <t>701848</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1305045</t>
+          <t>1302000</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>544685; 581177</t>
+          <t>544183; 582233</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>404283; 455547</t>
+          <t>403062; 451919</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>480953; 539617</t>
+          <t>573054; 625234</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623048; 649709</t>
+          <t>621767; 649815</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>480727; 527640</t>
+          <t>479420; 525459</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>763580; 825390</t>
+          <t>682551; 717750</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1177205; 1222892</t>
+          <t>1178033; 1224874</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>896556; 969824</t>
+          <t>897363; 970177</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1261216; 1369371</t>
+          <t>1267569; 1333660</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>420807</t>
+          <t>477425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>505423</t>
+          <t>573866</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>926230</t>
+          <t>1051291</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>546323; 597235</t>
+          <t>548217; 599596</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>671744; 705147</t>
+          <t>670124; 703876</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>198780; 587782</t>
+          <t>445337; 507099</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>622355; 673346</t>
+          <t>622673; 671193</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>765628; 791330</t>
+          <t>764873; 790696</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>482576; 527265</t>
+          <t>546908; 599851</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1186057; 1256442</t>
+          <t>1185282; 1254736</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1446141; 1486459</t>
+          <t>1446326; 1488558</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>570326; 1101346</t>
+          <t>1012247; 1092366</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2601246</t>
+          <t>2822793</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3167804</t>
+          <t>3233776</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5769048</t>
+          <t>6056569</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2749310; 2837390</t>
+          <t>2748463; 2839886</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2705454; 2799000</t>
+          <t>2707488; 2797267</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1990444; 2821953</t>
+          <t>2763611; 2884715</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3064325; 3144046</t>
+          <t>3062664; 3142480</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3049687; 3126251</t>
+          <t>3046994; 3125537</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2959067; 3249668</t>
+          <t>3189397; 3278648</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5836035; 5956632</t>
+          <t>5843356; 5955221</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5782206; 5902103</t>
+          <t>5779928; 5893636</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5003784; 6034223</t>
+          <t>5974747; 6136083</t>
         </is>
       </c>
     </row>
